--- a/artfynd/A 15389-2024 artfynd.xlsx
+++ b/artfynd/A 15389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119371068</v>
+        <v>119370949</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +700,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515093</v>
+        <v>515135</v>
       </c>
       <c r="R2" t="n">
-        <v>6659697</v>
+        <v>6659766</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +776,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>fuktstråk i 70ärig kulturskog</t>
+          <t>fuktstråk</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -811,6 +806,140 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119371068</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Snöån, Sundet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>515093</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6659697</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>fuktstråk i 70ärig kulturskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15389-2024 artfynd.xlsx
+++ b/artfynd/A 15389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119370949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -940,8 +950,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>